--- a/excel/Investavimas Gerda.xlsx
+++ b/excel/Investavimas Gerda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F97F47C-E2F0-4B1A-9545-7633BC745312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD04042-C48F-44CA-9B21-401F7AB126AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -255,6 +255,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -267,19 +276,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -596,54 +596,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="15" t="s">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
       <c r="U1" s="9"/>
-      <c r="V1" s="16" t="s">
+      <c r="V1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="16"/>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
-      <c r="AB1" s="16"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="18"/>
       <c r="AC1" s="10"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="12"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="15"/>
     </row>
     <row r="2" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
+      <c r="A2" s="17"/>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
@@ -732,13 +732,13 @@
       <c r="A3" s="5">
         <v>46173</v>
       </c>
-      <c r="B3" s="17">
-        <v>106.34</v>
-      </c>
-      <c r="C3" s="18">
-        <v>106.34</v>
-      </c>
-      <c r="D3" s="19">
+      <c r="B3" s="11">
+        <v>200.31</v>
+      </c>
+      <c r="C3" s="12">
+        <v>200.31</v>
+      </c>
+      <c r="D3" s="13">
         <f>(C3-B3)/B3</f>
         <v>0</v>
       </c>
@@ -754,27 +754,27 @@
       <c r="L3" s="2"/>
       <c r="M3" s="6"/>
       <c r="N3" s="4">
-        <f>A3</f>
+        <f t="shared" ref="N3:O5" si="0">A3</f>
         <v>46173</v>
       </c>
       <c r="O3" s="2">
-        <f>B3</f>
-        <v>106.34</v>
+        <f t="shared" si="0"/>
+        <v>200.31</v>
       </c>
       <c r="P3" s="2">
         <f>O3</f>
-        <v>106.34</v>
+        <v>200.31</v>
       </c>
       <c r="Q3" s="2">
         <f>C3</f>
-        <v>106.34</v>
+        <v>200.31</v>
       </c>
       <c r="R3" s="2">
-        <f t="shared" ref="R3" si="0">Q3-O3</f>
+        <f t="shared" ref="R3" si="1">Q3-O3</f>
         <v>0</v>
       </c>
       <c r="S3" s="7">
-        <f t="shared" ref="S3" si="1">R3/O3</f>
+        <f t="shared" ref="S3" si="2">R3/O3</f>
         <v>0</v>
       </c>
       <c r="T3" s="2">
@@ -787,23 +787,23 @@
         <v>46173</v>
       </c>
       <c r="W3" s="2">
-        <f t="shared" ref="W3" si="2">G3+O3</f>
-        <v>106.34</v>
+        <f t="shared" ref="W3" si="3">G3+O3</f>
+        <v>200.31</v>
       </c>
       <c r="X3" s="2">
         <f>W3</f>
-        <v>106.34</v>
+        <v>200.31</v>
       </c>
       <c r="Y3" s="2">
-        <f t="shared" ref="Y3" si="3">I3+Q3</f>
-        <v>106.34</v>
+        <f t="shared" ref="Y3" si="4">I3+Q3</f>
+        <v>200.31</v>
       </c>
       <c r="Z3" s="2">
-        <f t="shared" ref="Z3" si="4">Y3-W3</f>
+        <f t="shared" ref="Z3" si="5">Y3-W3</f>
         <v>0</v>
       </c>
       <c r="AA3" s="7">
-        <f t="shared" ref="AA3" si="5">Z3/W3</f>
+        <f t="shared" ref="AA3" si="6">Z3/W3</f>
         <v>0</v>
       </c>
       <c r="AB3" s="2">
@@ -823,15 +823,15 @@
       <c r="A4" s="5">
         <v>46203</v>
       </c>
-      <c r="B4" s="17">
-        <v>215.3</v>
-      </c>
-      <c r="C4" s="18">
+      <c r="B4" s="11">
+        <v>200.31</v>
+      </c>
+      <c r="C4" s="12">
         <v>240.3</v>
       </c>
-      <c r="D4" s="19">
-        <f t="shared" ref="D4:D5" si="6">(C4-B4)/B4</f>
-        <v>0.1161170459823502</v>
+      <c r="D4" s="13">
+        <f t="shared" ref="D4:D5" si="7">(C4-B4)/B4</f>
+        <v>0.19964055713643855</v>
       </c>
       <c r="F4" s="4">
         <f>A4</f>
@@ -845,32 +845,32 @@
       <c r="L4" s="2"/>
       <c r="M4" s="6"/>
       <c r="N4" s="4">
-        <f>A4</f>
+        <f t="shared" si="0"/>
         <v>46203</v>
       </c>
       <c r="O4" s="2">
-        <f>B4</f>
-        <v>215.3</v>
+        <f t="shared" si="0"/>
+        <v>200.31</v>
       </c>
       <c r="P4" s="2">
-        <f t="shared" ref="P4" si="7">O4-O3</f>
-        <v>108.96000000000001</v>
+        <f t="shared" ref="P4" si="8">O4-O3</f>
+        <v>0</v>
       </c>
       <c r="Q4" s="2">
         <f>C4</f>
         <v>240.3</v>
       </c>
       <c r="R4" s="2">
-        <f t="shared" ref="R4" si="8">Q4-O4</f>
-        <v>25</v>
+        <f t="shared" ref="R4" si="9">Q4-O4</f>
+        <v>39.990000000000009</v>
       </c>
       <c r="S4" s="7">
-        <f t="shared" ref="S4" si="9">R4/O4</f>
-        <v>0.1161170459823502</v>
+        <f t="shared" ref="S4" si="10">R4/O4</f>
+        <v>0.19964055713643855</v>
       </c>
       <c r="T4" s="2">
-        <f t="shared" ref="T4" si="10">R4-R3</f>
-        <v>25</v>
+        <f t="shared" ref="T4" si="11">R4-R3</f>
+        <v>39.990000000000009</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="4">
@@ -878,28 +878,28 @@
         <v>46203</v>
       </c>
       <c r="W4" s="2">
-        <f t="shared" ref="W4" si="11">G4+O4</f>
-        <v>215.3</v>
+        <f t="shared" ref="W4" si="12">G4+O4</f>
+        <v>200.31</v>
       </c>
       <c r="X4" s="2">
-        <f t="shared" ref="X4" si="12">W4-W3</f>
-        <v>108.96000000000001</v>
+        <f t="shared" ref="X4" si="13">W4-W3</f>
+        <v>0</v>
       </c>
       <c r="Y4" s="2">
-        <f t="shared" ref="Y4" si="13">I4+Q4</f>
+        <f t="shared" ref="Y4" si="14">I4+Q4</f>
         <v>240.3</v>
       </c>
       <c r="Z4" s="2">
-        <f t="shared" ref="Z4" si="14">Y4-W4</f>
-        <v>25</v>
+        <f t="shared" ref="Z4" si="15">Y4-W4</f>
+        <v>39.990000000000009</v>
       </c>
       <c r="AA4" s="7">
-        <f t="shared" ref="AA4" si="15">Z4/W4</f>
-        <v>0.1161170459823502</v>
+        <f t="shared" ref="AA4" si="16">Z4/W4</f>
+        <v>0.19964055713643855</v>
       </c>
       <c r="AB4" s="2">
-        <f t="shared" ref="AB4" si="16">Z4-Z3</f>
-        <v>25</v>
+        <f t="shared" ref="AB4" si="17">Z4-Z3</f>
+        <v>39.990000000000009</v>
       </c>
       <c r="AD4" s="4">
         <f>A4</f>
@@ -907,22 +907,22 @@
       </c>
       <c r="AE4" s="2">
         <f>(C4-B4)-(C3-B3)</f>
-        <v>25</v>
+        <v>39.990000000000009</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>46234</v>
       </c>
-      <c r="B5" s="17">
-        <v>215.3</v>
-      </c>
-      <c r="C5" s="18">
+      <c r="B5" s="11">
+        <v>200.31</v>
+      </c>
+      <c r="C5" s="12">
         <v>240.3</v>
       </c>
-      <c r="D5" s="19">
-        <f t="shared" si="6"/>
-        <v>0.1161170459823502</v>
+      <c r="D5" s="13">
+        <f t="shared" si="7"/>
+        <v>0.19964055713643855</v>
       </c>
       <c r="F5" s="4">
         <f>A5</f>
@@ -936,15 +936,15 @@
       <c r="L5" s="2"/>
       <c r="M5" s="6"/>
       <c r="N5" s="4">
-        <f>A5</f>
+        <f t="shared" si="0"/>
         <v>46234</v>
       </c>
       <c r="O5" s="2">
-        <f>B5</f>
-        <v>215.3</v>
+        <f t="shared" si="0"/>
+        <v>200.31</v>
       </c>
       <c r="P5" s="2">
-        <f t="shared" ref="P5" si="17">O5-O4</f>
+        <f t="shared" ref="P5" si="18">O5-O4</f>
         <v>0</v>
       </c>
       <c r="Q5" s="2">
@@ -952,15 +952,15 @@
         <v>240.3</v>
       </c>
       <c r="R5" s="2">
-        <f t="shared" ref="R5" si="18">Q5-O5</f>
-        <v>25</v>
+        <f t="shared" ref="R5" si="19">Q5-O5</f>
+        <v>39.990000000000009</v>
       </c>
       <c r="S5" s="7">
-        <f t="shared" ref="S5" si="19">R5/O5</f>
-        <v>0.1161170459823502</v>
+        <f t="shared" ref="S5" si="20">R5/O5</f>
+        <v>0.19964055713643855</v>
       </c>
       <c r="T5" s="2">
-        <f t="shared" ref="T5" si="20">R5-R4</f>
+        <f t="shared" ref="T5" si="21">R5-R4</f>
         <v>0</v>
       </c>
       <c r="U5" s="6"/>
@@ -969,27 +969,27 @@
         <v>46234</v>
       </c>
       <c r="W5" s="2">
-        <f t="shared" ref="W5" si="21">G5+O5</f>
-        <v>215.3</v>
+        <f t="shared" ref="W5" si="22">G5+O5</f>
+        <v>200.31</v>
       </c>
       <c r="X5" s="2">
-        <f t="shared" ref="X5" si="22">W5-W4</f>
+        <f t="shared" ref="X5" si="23">W5-W4</f>
         <v>0</v>
       </c>
       <c r="Y5" s="2">
-        <f t="shared" ref="Y5" si="23">I5+Q5</f>
+        <f t="shared" ref="Y5" si="24">I5+Q5</f>
         <v>240.3</v>
       </c>
       <c r="Z5" s="2">
-        <f t="shared" ref="Z5" si="24">Y5-W5</f>
-        <v>25</v>
+        <f t="shared" ref="Z5" si="25">Y5-W5</f>
+        <v>39.990000000000009</v>
       </c>
       <c r="AA5" s="7">
-        <f t="shared" ref="AA5" si="25">Z5/W5</f>
-        <v>0.1161170459823502</v>
+        <f t="shared" ref="AA5" si="26">Z5/W5</f>
+        <v>0.19964055713643855</v>
       </c>
       <c r="AB5" s="2">
-        <f t="shared" ref="AB5" si="26">Z5-Z4</f>
+        <f t="shared" ref="AB5" si="27">Z5-Z4</f>
         <v>0</v>
       </c>
       <c r="AD5" s="4">
@@ -999,6 +999,97 @@
       <c r="AE5" s="2">
         <f>(C5-B5)-(C4-B4)</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>46265</v>
+      </c>
+      <c r="B6" s="11">
+        <v>200.31</v>
+      </c>
+      <c r="C6" s="12">
+        <v>242.56</v>
+      </c>
+      <c r="D6" s="13">
+        <f t="shared" ref="D6" si="28">(C6-B6)/B6</f>
+        <v>0.21092306924267384</v>
+      </c>
+      <c r="F6" s="4">
+        <f>A6</f>
+        <v>46265</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="4">
+        <f t="shared" ref="N6" si="29">A6</f>
+        <v>46265</v>
+      </c>
+      <c r="O6" s="2">
+        <f t="shared" ref="O6" si="30">B6</f>
+        <v>200.31</v>
+      </c>
+      <c r="P6" s="2">
+        <f t="shared" ref="P6" si="31">O6-O5</f>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2">
+        <f>C6</f>
+        <v>242.56</v>
+      </c>
+      <c r="R6" s="2">
+        <f t="shared" ref="R6" si="32">Q6-O6</f>
+        <v>42.25</v>
+      </c>
+      <c r="S6" s="7">
+        <f t="shared" ref="S6" si="33">R6/O6</f>
+        <v>0.21092306924267384</v>
+      </c>
+      <c r="T6" s="2">
+        <f t="shared" ref="T6" si="34">R6-R5</f>
+        <v>2.2599999999999909</v>
+      </c>
+      <c r="U6" s="6"/>
+      <c r="V6" s="4">
+        <f>A6</f>
+        <v>46265</v>
+      </c>
+      <c r="W6" s="2">
+        <f t="shared" ref="W6" si="35">G6+O6</f>
+        <v>200.31</v>
+      </c>
+      <c r="X6" s="2">
+        <f t="shared" ref="X6" si="36">W6-W5</f>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="2">
+        <f t="shared" ref="Y6" si="37">I6+Q6</f>
+        <v>242.56</v>
+      </c>
+      <c r="Z6" s="2">
+        <f t="shared" ref="Z6" si="38">Y6-W6</f>
+        <v>42.25</v>
+      </c>
+      <c r="AA6" s="7">
+        <f t="shared" ref="AA6" si="39">Z6/W6</f>
+        <v>0.21092306924267384</v>
+      </c>
+      <c r="AB6" s="2">
+        <f t="shared" ref="AB6" si="40">Z6-Z5</f>
+        <v>2.2599999999999909</v>
+      </c>
+      <c r="AD6" s="4">
+        <f>A6</f>
+        <v>46265</v>
+      </c>
+      <c r="AE6" s="2">
+        <f>(C6-B6)-(C5-B5)</f>
+        <v>2.2599999999999909</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +1105,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="X3:X5" formula="1"/>
+    <ignoredError sqref="X3:X6" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>